--- a/xlsx/country_comparison/main_radical_redistr_pol_US_positive.xlsx
+++ b/xlsx/country_comparison/main_radical_redistr_pol_US_positive.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">Global climate scheme (GCS)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supports Int'l Climate Scheme (any variant)</t>
+    <t xml:space="preserve">Supports int'l climate scheme (any variant)</t>
   </si>
   <si>
     <t xml:space="preserve">Supports int'l tax on millionaires
